--- a/paper_tables/Table_1_Descriptive_Statistics.xlsx
+++ b/paper_tables/Table_1_Descriptive_Statistics.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descriptive_Stats" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Descriptive Statistics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +468,7 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -487,49 +487,49 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>std</t>
+          <t>Std Dev</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>Q1 (25%)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>Q3 (75%)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>Max</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>band_gap</t>
+          <t>Band Gap ($E_g$, eV)</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -560,7 +560,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>formation_energy</t>
+          <t>Formation Energy ($E_f$, eV/atom)</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>energy_hull</t>
+          <t>Energy Above Hull ($E_{\mathrm{hull}}$, eV/atom)</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -616,131 +616,131 @@
         <v>1.829</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>5.108</v>
+        <v>5.107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>bulk_modulus</t>
+          <t>Li Adsorption Energy ($E_{\mathrm{ads}}$, eV)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
         <v>115</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>57.789</v>
+        <v>-2.938</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>60.852</v>
+        <v>1.065</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>5</v>
+        <v>-7.102</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>24.05</v>
+        <v>-3.56</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>37.68</v>
+        <v>-2.946</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>70.39</v>
+        <v>-2.065</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>419.28</v>
+        <v>-0.819</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>shear_modulus</t>
+          <t>Bulk Modulus ($K$, GPa)</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>115</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>32.365</v>
+        <v>57.789</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>52.523</v>
+        <v>60.852</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1.32</v>
+        <v>5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>10.375</v>
+        <v>24.05</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>19.52</v>
+        <v>37.68</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>33.01</v>
+        <v>70.39</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>475.47</v>
+        <v>419.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>young_modulus</t>
+          <t>Shear Modulus ($G$, GPa)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
         <v>115</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>80.056</v>
+        <v>32.365</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>119.018</v>
+        <v>52.523</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3.873</v>
+        <v>1.32</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>27.373</v>
+        <v>10.375</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>52.595</v>
+        <v>19.52</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>80.69499999999999</v>
+        <v>33.01</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>1035.127</v>
+        <v>475.47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>E_ads_DFT_eV</t>
+          <t>Young's Modulus ($E$, GPa)</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>115</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>-2.938</v>
+        <v>80.056</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1.065</v>
+        <v>119.018</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-7.102</v>
+        <v>3.873</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-3.56</v>
+        <v>27.373</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>-2.946</v>
+        <v>52.595</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-2.065</v>
+        <v>80.69499999999999</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>-0.819</v>
+        <v>1035.127</v>
       </c>
     </row>
   </sheetData>
